--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
@@ -704,94 +704,94 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1218</v>
+        <v>1384</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>670</v>
+        <v>736</v>
       </c>
       <c r="G3" t="n">
-        <v>495</v>
+        <v>583</v>
       </c>
       <c r="H3" t="n">
-        <v>1713</v>
+        <v>1967</v>
       </c>
       <c r="I3" t="n">
-        <v>1516</v>
+        <v>1281</v>
       </c>
       <c r="J3" t="n">
-        <v>1858</v>
+        <v>1819</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>267</v>
+        <v>589</v>
       </c>
       <c r="R3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="S3" t="n">
-        <v>4044</v>
+        <v>4118</v>
       </c>
       <c r="T3" t="n">
-        <v>2491</v>
+        <v>2798</v>
       </c>
       <c r="U3" t="n">
-        <v>1491</v>
+        <v>1283</v>
       </c>
       <c r="V3" t="n">
-        <v>1763</v>
+        <v>1819</v>
       </c>
       <c r="W3" t="n">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="X3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB3" t="n">
         <v>3</v>
       </c>
       <c r="AC3" t="n">
-        <v>407</v>
+        <v>589</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>4054</v>
+        <v>4118</v>
       </c>
       <c r="AF3" t="n">
-        <v>2515</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="4">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D4" t="n">
         <v>38</v>
@@ -818,82 +818,82 @@
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="H4" t="n">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="I4" t="n">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="J4" t="n">
-        <v>513</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="T4" t="n">
-        <v>614</v>
+        <v>661</v>
       </c>
       <c r="U4" t="n">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="V4" t="n">
-        <v>514</v>
+        <v>446</v>
       </c>
       <c r="W4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X4" t="n">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="Y4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="AF4" t="n">
-        <v>615</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5">
@@ -908,40 +908,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1103</v>
+        <v>1173</v>
       </c>
       <c r="D5" t="n">
-        <v>847</v>
+        <v>911</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G5" t="n">
-        <v>824</v>
+        <v>908</v>
       </c>
       <c r="H5" t="n">
-        <v>1927</v>
+        <v>2081</v>
       </c>
       <c r="I5" t="n">
-        <v>2208</v>
+        <v>1831</v>
       </c>
       <c r="J5" t="n">
-        <v>3449</v>
+        <v>3389</v>
       </c>
       <c r="K5" t="n">
-        <v>92</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M5" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -950,34 +950,34 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>422</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6152</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4225</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1756</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3456</v>
+      </c>
+      <c r="W5" t="n">
+        <v>386</v>
+      </c>
+      <c r="X5" t="n">
         <v>95</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6010</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3715</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2208</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3445</v>
-      </c>
-      <c r="W5" t="n">
-        <v>96</v>
-      </c>
-      <c r="X5" t="n">
-        <v>88</v>
-      </c>
       <c r="Y5" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>95</v>
+        <v>422</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>6010</v>
+        <v>6181</v>
       </c>
       <c r="AF5" t="n">
-        <v>3714</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="6">
@@ -1010,31 +1010,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1127</v>
+        <v>1254</v>
       </c>
       <c r="D6" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="G6" t="n">
-        <v>576</v>
+        <v>667</v>
       </c>
       <c r="H6" t="n">
-        <v>1703</v>
+        <v>1921</v>
       </c>
       <c r="I6" t="n">
-        <v>1070</v>
+        <v>902</v>
       </c>
       <c r="J6" t="n">
-        <v>1615</v>
+        <v>1675</v>
       </c>
       <c r="K6" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1046,31 +1046,31 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>3058</v>
+        <v>3121</v>
       </c>
       <c r="T6" t="n">
-        <v>1988</v>
+        <v>2219</v>
       </c>
       <c r="U6" t="n">
-        <v>1070</v>
+        <v>902</v>
       </c>
       <c r="V6" t="n">
-        <v>1620</v>
+        <v>1675</v>
       </c>
       <c r="W6" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>246</v>
+        <v>440</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
-        <v>3058</v>
+        <v>3121</v>
       </c>
       <c r="AF6" t="n">
-        <v>1988</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="7">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>307</v>
+        <v>433</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1124,82 +1124,82 @@
         <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="H7" t="n">
-        <v>408</v>
+        <v>555</v>
       </c>
       <c r="I7" t="n">
-        <v>542</v>
+        <v>448</v>
       </c>
       <c r="J7" t="n">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>93</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1121</v>
+      </c>
+      <c r="T7" t="n">
+        <v>659</v>
+      </c>
+      <c r="U7" t="n">
+        <v>449</v>
+      </c>
+      <c r="V7" t="n">
+        <v>544</v>
+      </c>
+      <c r="W7" t="n">
         <v>5</v>
       </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>44</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1105</v>
-      </c>
-      <c r="T7" t="n">
-        <v>550</v>
-      </c>
-      <c r="U7" t="n">
-        <v>543</v>
-      </c>
-      <c r="V7" t="n">
-        <v>490</v>
-      </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1105</v>
+        <v>1121</v>
       </c>
       <c r="AF7" t="n">
-        <v>549</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="D8" t="n">
         <v>24</v>
@@ -1223,31 +1223,31 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="G8" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="H8" t="n">
-        <v>322</v>
+        <v>364</v>
       </c>
       <c r="I8" t="n">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="J8" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1256,34 +1256,34 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="T8" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="U8" t="n">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="V8" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1292,16 +1292,16 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="AF8" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9">
@@ -1316,40 +1316,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>830</v>
+        <v>914</v>
       </c>
       <c r="D9" t="n">
-        <v>680</v>
+        <v>742</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="H9" t="n">
-        <v>1287</v>
+        <v>1429</v>
       </c>
       <c r="I9" t="n">
-        <v>2210</v>
+        <v>2105</v>
       </c>
       <c r="J9" t="n">
-        <v>2073</v>
+        <v>1928</v>
       </c>
       <c r="K9" t="n">
-        <v>158</v>
+        <v>223</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1358,34 +1358,34 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>261</v>
       </c>
       <c r="R9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4573</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2432</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1928</v>
+      </c>
+      <c r="W9" t="n">
+        <v>229</v>
+      </c>
+      <c r="X9" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4540</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2305</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2210</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2074</v>
-      </c>
-      <c r="W9" t="n">
-        <v>155</v>
-      </c>
-      <c r="X9" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
@@ -1394,16 +1394,16 @@
         <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>61</v>
+        <v>261</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
-        <v>4539</v>
+        <v>4574</v>
       </c>
       <c r="AF9" t="n">
-        <v>2302</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="10">
@@ -1418,94 +1418,94 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1133</v>
+        <v>1245</v>
       </c>
       <c r="D10" t="n">
-        <v>777</v>
+        <v>829</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G10" t="n">
-        <v>1186</v>
+        <v>1332</v>
       </c>
       <c r="H10" t="n">
-        <v>2319</v>
+        <v>2577</v>
       </c>
       <c r="I10" t="n">
-        <v>3079</v>
+        <v>2889</v>
       </c>
       <c r="J10" t="n">
-        <v>2603</v>
+        <v>2279</v>
       </c>
       <c r="K10" t="n">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>5884</v>
+        <v>5969</v>
       </c>
       <c r="T10" t="n">
-        <v>2772</v>
+        <v>3042</v>
       </c>
       <c r="U10" t="n">
-        <v>3079</v>
+        <v>2890</v>
       </c>
       <c r="V10" t="n">
-        <v>2603</v>
+        <v>2279</v>
       </c>
       <c r="W10" t="n">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="X10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Y10" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>5884</v>
+        <v>5969</v>
       </c>
       <c r="AF10" t="n">
-        <v>2772</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="11">
@@ -1520,37 +1520,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>375</v>
+        <v>441</v>
       </c>
       <c r="D11" t="n">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G11" t="n">
-        <v>449</v>
+        <v>494</v>
       </c>
       <c r="H11" t="n">
-        <v>824</v>
+        <v>935</v>
       </c>
       <c r="I11" t="n">
-        <v>3915</v>
+        <v>3660</v>
       </c>
       <c r="J11" t="n">
-        <v>3813</v>
+        <v>3861</v>
       </c>
       <c r="K11" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="L11" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1562,31 +1562,31 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="R11" t="n">
         <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>7944</v>
+        <v>8009</v>
       </c>
       <c r="T11" t="n">
-        <v>3900</v>
+        <v>4199</v>
       </c>
       <c r="U11" t="n">
-        <v>3918</v>
+        <v>3661</v>
       </c>
       <c r="V11" t="n">
-        <v>3813</v>
+        <v>3854</v>
       </c>
       <c r="W11" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="X11" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="Y11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -1598,16 +1598,16 @@
         <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="AD11" t="n">
         <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>7944</v>
+        <v>8009</v>
       </c>
       <c r="AF11" t="n">
-        <v>3900</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="12">
@@ -1622,40 +1622,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>624</v>
+        <v>682</v>
       </c>
       <c r="D12" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G12" t="n">
-        <v>557</v>
+        <v>688</v>
       </c>
       <c r="H12" t="n">
-        <v>1181</v>
+        <v>1370</v>
       </c>
       <c r="I12" t="n">
-        <v>2373</v>
+        <v>2154</v>
       </c>
       <c r="J12" t="n">
-        <v>2316</v>
+        <v>2397</v>
       </c>
       <c r="K12" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="L12" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>3</v>
@@ -1664,34 +1664,34 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>5119</v>
+        <v>5162</v>
       </c>
       <c r="T12" t="n">
-        <v>2591</v>
+        <v>2880</v>
       </c>
       <c r="U12" t="n">
-        <v>2373</v>
+        <v>2159</v>
       </c>
       <c r="V12" t="n">
-        <v>2314</v>
+        <v>2397</v>
       </c>
       <c r="W12" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="X12" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="Y12" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
         <v>3</v>
@@ -1700,16 +1700,16 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>5119</v>
+        <v>5162</v>
       </c>
       <c r="AF12" t="n">
-        <v>2591</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="13">
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>556</v>
+        <v>686</v>
       </c>
       <c r="D13" t="n">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1736,82 +1736,82 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>269</v>
+        <v>324</v>
       </c>
       <c r="H13" t="n">
-        <v>825</v>
+        <v>1010</v>
       </c>
       <c r="I13" t="n">
-        <v>1273</v>
+        <v>1148</v>
       </c>
       <c r="J13" t="n">
-        <v>899</v>
+        <v>800</v>
       </c>
       <c r="K13" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>63</v>
+        <v>229</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S13" t="n">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="T13" t="n">
-        <v>1080</v>
+        <v>1216</v>
       </c>
       <c r="U13" t="n">
-        <v>1274</v>
+        <v>1150</v>
       </c>
       <c r="V13" t="n">
-        <v>901</v>
+        <v>800</v>
       </c>
       <c r="W13" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="X13" t="n">
         <v>30</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="AF13" t="n">
-        <v>1079</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="14">
@@ -1826,94 +1826,94 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2011</v>
+        <v>2179</v>
       </c>
       <c r="D14" t="n">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>1571</v>
+        <v>1737</v>
       </c>
       <c r="H14" t="n">
-        <v>3582</v>
+        <v>3916</v>
       </c>
       <c r="I14" t="n">
-        <v>3667</v>
+        <v>3161</v>
       </c>
       <c r="J14" t="n">
-        <v>5078</v>
+        <v>5121</v>
       </c>
       <c r="K14" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="L14" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="M14" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S14" t="n">
-        <v>9254</v>
+        <v>9452</v>
       </c>
       <c r="T14" t="n">
-        <v>5465</v>
+        <v>6129</v>
       </c>
       <c r="U14" t="n">
-        <v>3402</v>
+        <v>2895</v>
       </c>
       <c r="V14" t="n">
-        <v>5075</v>
+        <v>5121</v>
       </c>
       <c r="W14" t="n">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="X14" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="Y14" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
-        <v>8899</v>
+        <v>9097</v>
       </c>
       <c r="AF14" t="n">
-        <v>5376</v>
+        <v>6041</v>
       </c>
     </row>
     <row r="15">
@@ -1928,37 +1928,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="D15" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="H15" t="n">
-        <v>656</v>
+        <v>710</v>
       </c>
       <c r="I15" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="J15" t="n">
-        <v>713</v>
+        <v>664</v>
       </c>
       <c r="K15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1970,31 +1970,31 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="T15" t="n">
-        <v>779</v>
+        <v>833</v>
       </c>
       <c r="U15" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="V15" t="n">
-        <v>713</v>
+        <v>664</v>
       </c>
       <c r="W15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2006,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="AF15" t="n">
-        <v>779</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16">
@@ -2033,7 +2033,7 @@
         <v>109</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -2042,22 +2042,22 @@
         <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H16" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I16" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="J16" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
@@ -2078,22 +2078,22 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="T16" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="U16" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="V16" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
         <v>2</v>
@@ -2114,10 +2114,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="AF16" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17">
@@ -2132,94 +2132,94 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="D17" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="G17" t="n">
-        <v>446</v>
+        <v>511</v>
       </c>
       <c r="H17" t="n">
-        <v>901</v>
+        <v>1034</v>
       </c>
       <c r="I17" t="n">
-        <v>1347</v>
+        <v>1236</v>
       </c>
       <c r="J17" t="n">
-        <v>1255</v>
+        <v>1149</v>
       </c>
       <c r="K17" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
         <v>6</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>355</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2781</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1541</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1230</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1127</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
         <v>6</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>104</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2753</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1400</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1348</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1255</v>
-      </c>
-      <c r="W17" t="n">
-        <v>32</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
       <c r="AA17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>104</v>
+        <v>404</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>2753</v>
+        <v>2784</v>
       </c>
       <c r="AF17" t="n">
-        <v>1399</v>
+        <v>1550</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,162 +417,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah Usaha dalam Keluarga</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -722,19 +710,19 @@
         <v>1967</v>
       </c>
       <c r="I3" t="n">
-        <v>1281</v>
+        <v>1169</v>
       </c>
       <c r="J3" t="n">
-        <v>1819</v>
+        <v>2221</v>
       </c>
       <c r="K3" t="n">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="L3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -752,25 +740,25 @@
         <v>23</v>
       </c>
       <c r="S3" t="n">
-        <v>4118</v>
+        <v>4130</v>
       </c>
       <c r="T3" t="n">
-        <v>2798</v>
+        <v>2924</v>
       </c>
       <c r="U3" t="n">
-        <v>1283</v>
+        <v>1169</v>
       </c>
       <c r="V3" t="n">
-        <v>1819</v>
+        <v>2221</v>
       </c>
       <c r="W3" t="n">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="X3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -788,10 +776,10 @@
         <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>4118</v>
+        <v>4130</v>
       </c>
       <c r="AF3" t="n">
-        <v>2795</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="4">
@@ -824,52 +812,52 @@
         <v>378</v>
       </c>
       <c r="I4" t="n">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="J4" t="n">
-        <v>433</v>
+        <v>507</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L4" t="n">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="T4" t="n">
-        <v>661</v>
+        <v>744</v>
       </c>
       <c r="U4" t="n">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="V4" t="n">
-        <v>446</v>
+        <v>507</v>
       </c>
       <c r="W4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="X4" t="n">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -878,22 +866,22 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="AF4" t="n">
-        <v>670</v>
+        <v>744</v>
       </c>
     </row>
     <row r="5">
@@ -926,22 +914,22 @@
         <v>2081</v>
       </c>
       <c r="I5" t="n">
-        <v>1831</v>
+        <v>1605</v>
       </c>
       <c r="J5" t="n">
-        <v>3389</v>
+        <v>3789</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>104</v>
       </c>
       <c r="L5" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -950,34 +938,34 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>422</v>
+        <v>543</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>6152</v>
+        <v>6241</v>
       </c>
       <c r="T5" t="n">
-        <v>4225</v>
+        <v>4550</v>
       </c>
       <c r="U5" t="n">
-        <v>1756</v>
+        <v>1605</v>
       </c>
       <c r="V5" t="n">
-        <v>3456</v>
+        <v>3789</v>
       </c>
       <c r="W5" t="n">
-        <v>386</v>
+        <v>104</v>
       </c>
       <c r="X5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="Y5" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -986,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>422</v>
+        <v>543</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>6181</v>
+        <v>6240</v>
       </c>
       <c r="AF5" t="n">
-        <v>4330</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="6">
@@ -1028,19 +1016,19 @@
         <v>1921</v>
       </c>
       <c r="I6" t="n">
-        <v>902</v>
+        <v>805</v>
       </c>
       <c r="J6" t="n">
-        <v>1675</v>
+        <v>1886</v>
       </c>
       <c r="K6" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1058,25 +1046,25 @@
         <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>3121</v>
+        <v>3158</v>
       </c>
       <c r="T6" t="n">
-        <v>2219</v>
+        <v>2353</v>
       </c>
       <c r="U6" t="n">
-        <v>902</v>
+        <v>806</v>
       </c>
       <c r="V6" t="n">
-        <v>1675</v>
+        <v>1886</v>
       </c>
       <c r="W6" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1094,10 +1082,10 @@
         <v>8</v>
       </c>
       <c r="AE6" t="n">
-        <v>3121</v>
+        <v>3158</v>
       </c>
       <c r="AF6" t="n">
-        <v>2219</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="7">
@@ -1130,19 +1118,19 @@
         <v>555</v>
       </c>
       <c r="I7" t="n">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="J7" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1160,25 +1148,25 @@
         <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="T7" t="n">
-        <v>659</v>
+        <v>693</v>
       </c>
       <c r="U7" t="n">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="V7" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="W7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1196,10 +1184,10 @@
         <v>8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="AF7" t="n">
-        <v>658</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
@@ -1232,25 +1220,25 @@
         <v>364</v>
       </c>
       <c r="I8" t="n">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="J8" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1262,31 +1250,31 @@
         <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="T8" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="U8" t="n">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="V8" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1298,10 +1286,10 @@
         <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AF8" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
     </row>
     <row r="9">
@@ -1334,22 +1322,22 @@
         <v>1429</v>
       </c>
       <c r="I9" t="n">
-        <v>2105</v>
+        <v>2049</v>
       </c>
       <c r="J9" t="n">
-        <v>1928</v>
+        <v>1986</v>
       </c>
       <c r="K9" t="n">
         <v>223</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1358,34 +1346,34 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="R9" t="n">
         <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>4573</v>
+        <v>4596</v>
       </c>
       <c r="T9" t="n">
-        <v>2432</v>
+        <v>2510</v>
       </c>
       <c r="U9" t="n">
-        <v>2100</v>
+        <v>2049</v>
       </c>
       <c r="V9" t="n">
-        <v>1928</v>
+        <v>1990</v>
       </c>
       <c r="W9" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="X9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
         <v>2</v>
@@ -1394,16 +1382,16 @@
         <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="AD9" t="n">
         <v>9</v>
       </c>
       <c r="AE9" t="n">
-        <v>4574</v>
+        <v>4596</v>
       </c>
       <c r="AF9" t="n">
-        <v>2438</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="10">
@@ -1436,76 +1424,76 @@
         <v>2577</v>
       </c>
       <c r="I10" t="n">
-        <v>2889</v>
+        <v>2813</v>
       </c>
       <c r="J10" t="n">
-        <v>2279</v>
+        <v>2427</v>
       </c>
       <c r="K10" t="n">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>5969</v>
+        <v>5997</v>
       </c>
       <c r="T10" t="n">
-        <v>3042</v>
+        <v>3149</v>
       </c>
       <c r="U10" t="n">
-        <v>2890</v>
+        <v>2808</v>
       </c>
       <c r="V10" t="n">
-        <v>2279</v>
+        <v>2424</v>
       </c>
       <c r="W10" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="X10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Y10" t="n">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>5969</v>
+        <v>5997</v>
       </c>
       <c r="AF10" t="n">
-        <v>3040</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="11">
@@ -1538,19 +1526,19 @@
         <v>935</v>
       </c>
       <c r="I11" t="n">
-        <v>3660</v>
+        <v>3560</v>
       </c>
       <c r="J11" t="n">
-        <v>3861</v>
+        <v>3868</v>
       </c>
       <c r="K11" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1562,31 +1550,31 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>228</v>
+        <v>456</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>8009</v>
+        <v>8064</v>
       </c>
       <c r="T11" t="n">
-        <v>4199</v>
+        <v>4368</v>
       </c>
       <c r="U11" t="n">
-        <v>3661</v>
+        <v>3560</v>
       </c>
       <c r="V11" t="n">
-        <v>3854</v>
+        <v>3868</v>
       </c>
       <c r="W11" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="X11" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -1598,16 +1586,16 @@
         <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>227</v>
+        <v>456</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>8009</v>
+        <v>8064</v>
       </c>
       <c r="AF11" t="n">
-        <v>4198</v>
+        <v>4368</v>
       </c>
     </row>
     <row r="12">
@@ -1640,25 +1628,25 @@
         <v>1370</v>
       </c>
       <c r="I12" t="n">
-        <v>2154</v>
+        <v>2077</v>
       </c>
       <c r="J12" t="n">
-        <v>2397</v>
+        <v>2487</v>
       </c>
       <c r="K12" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="L12" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1670,31 +1658,31 @@
         <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>5162</v>
+        <v>5177</v>
       </c>
       <c r="T12" t="n">
-        <v>2880</v>
+        <v>2983</v>
       </c>
       <c r="U12" t="n">
-        <v>2159</v>
+        <v>2077</v>
       </c>
       <c r="V12" t="n">
-        <v>2397</v>
+        <v>2487</v>
       </c>
       <c r="W12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="X12" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="Y12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1706,10 +1694,10 @@
         <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>5162</v>
+        <v>5177</v>
       </c>
       <c r="AF12" t="n">
-        <v>2874</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="13">
@@ -1742,22 +1730,22 @@
         <v>1010</v>
       </c>
       <c r="I13" t="n">
-        <v>1148</v>
+        <v>1115</v>
       </c>
       <c r="J13" t="n">
-        <v>800</v>
+        <v>844</v>
       </c>
       <c r="K13" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="L13" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1766,34 +1754,34 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="R13" t="n">
         <v>16</v>
       </c>
       <c r="S13" t="n">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="T13" t="n">
-        <v>1216</v>
+        <v>1266</v>
       </c>
       <c r="U13" t="n">
-        <v>1150</v>
+        <v>1115</v>
       </c>
       <c r="V13" t="n">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="W13" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="X13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Y13" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>3</v>
@@ -1802,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AD13" t="n">
         <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="AF13" t="n">
-        <v>1216</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="14">
@@ -1844,22 +1832,22 @@
         <v>3916</v>
       </c>
       <c r="I14" t="n">
-        <v>3161</v>
+        <v>2948</v>
       </c>
       <c r="J14" t="n">
-        <v>5121</v>
+        <v>5564</v>
       </c>
       <c r="K14" t="n">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="L14" t="n">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="M14" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>11</v>
@@ -1868,34 +1856,34 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S14" t="n">
-        <v>9452</v>
+        <v>9558</v>
       </c>
       <c r="T14" t="n">
-        <v>6129</v>
+        <v>6511</v>
       </c>
       <c r="U14" t="n">
-        <v>2895</v>
+        <v>2682</v>
       </c>
       <c r="V14" t="n">
-        <v>5121</v>
+        <v>5561</v>
       </c>
       <c r="W14" t="n">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="X14" t="n">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
         <v>11</v>
@@ -1904,16 +1892,16 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>9097</v>
+        <v>9203</v>
       </c>
       <c r="AF14" t="n">
-        <v>6041</v>
+        <v>6424</v>
       </c>
     </row>
     <row r="15">
@@ -1946,13 +1934,13 @@
         <v>710</v>
       </c>
       <c r="I15" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="J15" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1976,19 +1964,19 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="T15" t="n">
-        <v>833</v>
+        <v>886</v>
       </c>
       <c r="U15" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="V15" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="W15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2012,10 +2000,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AF15" t="n">
-        <v>833</v>
+        <v>886</v>
       </c>
     </row>
     <row r="16">
@@ -2048,19 +2036,19 @@
         <v>302</v>
       </c>
       <c r="I16" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J16" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="K16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2075,28 +2063,28 @@
         <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>622</v>
       </c>
       <c r="T16" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="U16" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="V16" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="W16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2111,13 +2099,13 @@
         <v>20</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>622</v>
       </c>
       <c r="AF16" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17">
@@ -2150,76 +2138,76 @@
         <v>1034</v>
       </c>
       <c r="I17" t="n">
-        <v>1236</v>
+        <v>1162</v>
       </c>
       <c r="J17" t="n">
-        <v>1149</v>
+        <v>1195</v>
       </c>
       <c r="K17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="R17" t="n">
         <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>2781</v>
+        <v>2805</v>
       </c>
       <c r="T17" t="n">
-        <v>1541</v>
+        <v>1640</v>
       </c>
       <c r="U17" t="n">
-        <v>1230</v>
+        <v>1163</v>
       </c>
       <c r="V17" t="n">
-        <v>1127</v>
+        <v>1195</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AD17" t="n">
         <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>2784</v>
+        <v>2804</v>
       </c>
       <c r="AF17" t="n">
-        <v>1550</v>
+        <v>1638</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
@@ -692,94 +692,94 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1384</v>
+        <v>1836</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>736</v>
+        <v>830</v>
       </c>
       <c r="G3" t="n">
-        <v>583</v>
+        <v>877</v>
       </c>
       <c r="H3" t="n">
-        <v>1967</v>
+        <v>2713</v>
       </c>
       <c r="I3" t="n">
-        <v>1169</v>
+        <v>643</v>
       </c>
       <c r="J3" t="n">
-        <v>2221</v>
+        <v>2752</v>
       </c>
       <c r="K3" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>589</v>
+        <v>730</v>
       </c>
       <c r="R3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S3" t="n">
-        <v>4130</v>
+        <v>4258</v>
       </c>
       <c r="T3" t="n">
-        <v>2924</v>
+        <v>3560</v>
       </c>
       <c r="U3" t="n">
-        <v>1169</v>
+        <v>643</v>
       </c>
       <c r="V3" t="n">
-        <v>2221</v>
+        <v>2754</v>
       </c>
       <c r="W3" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="X3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AB3" t="n">
         <v>3</v>
       </c>
       <c r="AC3" t="n">
-        <v>589</v>
+        <v>730</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>4130</v>
+        <v>4258</v>
       </c>
       <c r="AF3" t="n">
-        <v>2924</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="4">
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>166</v>
+        <v>315</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>212</v>
+        <v>483</v>
       </c>
       <c r="H4" t="n">
-        <v>378</v>
+        <v>798</v>
       </c>
       <c r="I4" t="n">
-        <v>410</v>
+        <v>184</v>
       </c>
       <c r="J4" t="n">
-        <v>507</v>
+        <v>857</v>
       </c>
       <c r="K4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -836,31 +836,31 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="R4" t="n">
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>1420</v>
+        <v>1490</v>
       </c>
       <c r="T4" t="n">
-        <v>744</v>
+        <v>1107</v>
       </c>
       <c r="U4" t="n">
-        <v>410</v>
+        <v>184</v>
       </c>
       <c r="V4" t="n">
-        <v>507</v>
+        <v>857</v>
       </c>
       <c r="W4" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -872,16 +872,16 @@
         <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="AD4" t="n">
         <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1420</v>
+        <v>1490</v>
       </c>
       <c r="AF4" t="n">
-        <v>744</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="5">
@@ -896,73 +896,73 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1173</v>
+        <v>1596</v>
       </c>
       <c r="D5" t="n">
-        <v>911</v>
+        <v>1226</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>383</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1345</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2941</v>
+      </c>
+      <c r="I5" t="n">
+        <v>957</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4368</v>
+      </c>
+      <c r="K5" t="n">
+        <v>399</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" t="n">
+        <v>73</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>588</v>
+      </c>
+      <c r="R5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="n">
-        <v>288</v>
-      </c>
-      <c r="G5" t="n">
-        <v>908</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2081</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1605</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3789</v>
-      </c>
-      <c r="K5" t="n">
-        <v>104</v>
-      </c>
-      <c r="L5" t="n">
-        <v>86</v>
-      </c>
-      <c r="M5" t="n">
-        <v>113</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>543</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
-        <v>6241</v>
+        <v>6487</v>
       </c>
       <c r="T5" t="n">
-        <v>4550</v>
+        <v>5430</v>
       </c>
       <c r="U5" t="n">
-        <v>1605</v>
+        <v>959</v>
       </c>
       <c r="V5" t="n">
-        <v>3789</v>
+        <v>4368</v>
       </c>
       <c r="W5" t="n">
-        <v>104</v>
+        <v>399</v>
       </c>
       <c r="X5" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="Y5" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -974,16 +974,16 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>6240</v>
+        <v>6487</v>
       </c>
       <c r="AF5" t="n">
-        <v>4550</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="6">
@@ -998,94 +998,94 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1254</v>
+        <v>1707</v>
       </c>
       <c r="D6" t="n">
-        <v>212</v>
+        <v>266</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="G6" t="n">
-        <v>667</v>
+        <v>912</v>
       </c>
       <c r="H6" t="n">
-        <v>1921</v>
+        <v>2619</v>
       </c>
       <c r="I6" t="n">
-        <v>805</v>
+        <v>382</v>
       </c>
       <c r="J6" t="n">
-        <v>1886</v>
+        <v>2276</v>
       </c>
       <c r="K6" t="n">
+        <v>121</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>22</v>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>13</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>3158</v>
+        <v>3306</v>
       </c>
       <c r="T6" t="n">
-        <v>2353</v>
+        <v>2924</v>
       </c>
       <c r="U6" t="n">
-        <v>806</v>
+        <v>383</v>
       </c>
       <c r="V6" t="n">
-        <v>1886</v>
+        <v>2276</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>3158</v>
+        <v>3306</v>
       </c>
       <c r="AF6" t="n">
-        <v>2352</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="7">
@@ -1100,37 +1100,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>433</v>
+        <v>653</v>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="H7" t="n">
-        <v>555</v>
+        <v>831</v>
       </c>
       <c r="I7" t="n">
-        <v>421</v>
+        <v>310</v>
       </c>
       <c r="J7" t="n">
-        <v>558</v>
+        <v>694</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1142,31 +1142,31 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="R7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1158</v>
+      </c>
+      <c r="T7" t="n">
+        <v>832</v>
+      </c>
+      <c r="U7" t="n">
+        <v>310</v>
+      </c>
+      <c r="V7" t="n">
+        <v>694</v>
+      </c>
+      <c r="W7" t="n">
         <v>8</v>
       </c>
-      <c r="S7" t="n">
-        <v>1134</v>
-      </c>
-      <c r="T7" t="n">
-        <v>693</v>
-      </c>
-      <c r="U7" t="n">
-        <v>422</v>
-      </c>
-      <c r="V7" t="n">
-        <v>558</v>
-      </c>
-      <c r="W7" t="n">
-        <v>31</v>
-      </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="AF7" t="n">
-        <v>692</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -1202,94 +1202,94 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>214</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="G8" t="n">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="H8" t="n">
-        <v>364</v>
+        <v>506</v>
       </c>
       <c r="I8" t="n">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="J8" t="n">
-        <v>504</v>
+        <v>644</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>133</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1065</v>
+      </c>
+      <c r="T8" t="n">
+        <v>784</v>
+      </c>
+      <c r="U8" t="n">
+        <v>280</v>
+      </c>
+      <c r="V8" t="n">
+        <v>644</v>
+      </c>
+      <c r="W8" t="n">
         <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>112</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1019</v>
-      </c>
-      <c r="T8" t="n">
-        <v>634</v>
-      </c>
-      <c r="U8" t="n">
-        <v>384</v>
-      </c>
-      <c r="V8" t="n">
-        <v>504</v>
-      </c>
-      <c r="W8" t="n">
-        <v>10</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1019</v>
+        <v>1065</v>
       </c>
       <c r="AF8" t="n">
-        <v>634</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9">
@@ -1304,94 +1304,94 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>914</v>
+        <v>1307</v>
       </c>
       <c r="D9" t="n">
-        <v>742</v>
+        <v>953</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="G9" t="n">
-        <v>515</v>
+        <v>796</v>
       </c>
       <c r="H9" t="n">
-        <v>1429</v>
+        <v>2103</v>
       </c>
       <c r="I9" t="n">
-        <v>2049</v>
+        <v>1630</v>
       </c>
       <c r="J9" t="n">
-        <v>1986</v>
+        <v>2443</v>
       </c>
       <c r="K9" t="n">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>4596</v>
+        <v>4810</v>
       </c>
       <c r="T9" t="n">
-        <v>2510</v>
+        <v>3153</v>
       </c>
       <c r="U9" t="n">
-        <v>2049</v>
+        <v>1630</v>
       </c>
       <c r="V9" t="n">
-        <v>1990</v>
+        <v>2443</v>
       </c>
       <c r="W9" t="n">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="X9" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AB9" t="n">
         <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>277</v>
+        <v>378</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>4596</v>
+        <v>4810</v>
       </c>
       <c r="AF9" t="n">
-        <v>2510</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="10">
@@ -1406,94 +1406,94 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1245</v>
+        <v>1904</v>
       </c>
       <c r="D10" t="n">
-        <v>829</v>
+        <v>1146</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G10" t="n">
-        <v>1332</v>
+        <v>2320</v>
       </c>
       <c r="H10" t="n">
-        <v>2577</v>
+        <v>4224</v>
       </c>
       <c r="I10" t="n">
-        <v>2813</v>
+        <v>1980</v>
       </c>
       <c r="J10" t="n">
-        <v>2427</v>
+        <v>3260</v>
       </c>
       <c r="K10" t="n">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>531</v>
+        <v>577</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>5997</v>
+        <v>6348</v>
       </c>
       <c r="T10" t="n">
-        <v>3149</v>
+        <v>4331</v>
       </c>
       <c r="U10" t="n">
-        <v>2808</v>
+        <v>1980</v>
       </c>
       <c r="V10" t="n">
-        <v>2424</v>
+        <v>3260</v>
       </c>
       <c r="W10" t="n">
-        <v>103</v>
+        <v>295</v>
       </c>
       <c r="X10" t="n">
         <v>37</v>
       </c>
       <c r="Y10" t="n">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>531</v>
+        <v>577</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>5997</v>
+        <v>6347</v>
       </c>
       <c r="AF10" t="n">
-        <v>3152</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="11">
@@ -1508,94 +1508,94 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>441</v>
+        <v>682</v>
       </c>
       <c r="D11" t="n">
-        <v>277</v>
+        <v>371</v>
       </c>
       <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>149</v>
+      </c>
+      <c r="G11" t="n">
+        <v>715</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1397</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2620</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5034</v>
+      </c>
+      <c r="K11" t="n">
+        <v>48</v>
+      </c>
+      <c r="L11" t="n">
+        <v>178</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="F11" t="n">
-        <v>121</v>
-      </c>
-      <c r="G11" t="n">
-        <v>494</v>
-      </c>
-      <c r="H11" t="n">
-        <v>935</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3560</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3868</v>
-      </c>
-      <c r="K11" t="n">
-        <v>28</v>
-      </c>
-      <c r="L11" t="n">
-        <v>136</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>542</v>
+      </c>
+      <c r="R11" t="n">
         <v>6</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>456</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
+        <v>8450</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5652</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2620</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5034</v>
+      </c>
+      <c r="W11" t="n">
+        <v>48</v>
+      </c>
+      <c r="X11" t="n">
+        <v>176</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>5</v>
       </c>
-      <c r="S11" t="n">
-        <v>8064</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4368</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3560</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3868</v>
-      </c>
-      <c r="W11" t="n">
-        <v>28</v>
-      </c>
-      <c r="X11" t="n">
-        <v>136</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>542</v>
+      </c>
+      <c r="AD11" t="n">
         <v>6</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>456</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>5</v>
-      </c>
       <c r="AE11" t="n">
-        <v>8064</v>
+        <v>8448</v>
       </c>
       <c r="AF11" t="n">
-        <v>4368</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="12">
@@ -1610,94 +1610,94 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>682</v>
+        <v>974</v>
       </c>
       <c r="D12" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>269</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1099</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1416</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3241</v>
+      </c>
+      <c r="K12" t="n">
+        <v>37</v>
+      </c>
+      <c r="L12" t="n">
+        <v>148</v>
+      </c>
+      <c r="M12" t="n">
+        <v>55</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>6</v>
       </c>
-      <c r="F12" t="n">
-        <v>214</v>
-      </c>
-      <c r="G12" t="n">
-        <v>688</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1370</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2077</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2487</v>
-      </c>
-      <c r="K12" t="n">
-        <v>73</v>
-      </c>
-      <c r="L12" t="n">
-        <v>117</v>
-      </c>
-      <c r="M12" t="n">
-        <v>43</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>453</v>
+      </c>
+      <c r="R12" t="n">
         <v>5</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>371</v>
-      </c>
-      <c r="R12" t="n">
-        <v>4</v>
-      </c>
       <c r="S12" t="n">
-        <v>5177</v>
+        <v>5361</v>
       </c>
       <c r="T12" t="n">
-        <v>2983</v>
+        <v>3797</v>
       </c>
       <c r="U12" t="n">
-        <v>2077</v>
+        <v>1418</v>
       </c>
       <c r="V12" t="n">
-        <v>2487</v>
+        <v>3241</v>
       </c>
       <c r="W12" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="X12" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="Y12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>453</v>
+      </c>
+      <c r="AD12" t="n">
         <v>5</v>
       </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>371</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4</v>
-      </c>
       <c r="AE12" t="n">
-        <v>5177</v>
+        <v>5361</v>
       </c>
       <c r="AF12" t="n">
-        <v>2983</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="13">
@@ -1712,94 +1712,94 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>686</v>
+        <v>1040</v>
       </c>
       <c r="D13" t="n">
-        <v>254</v>
+        <v>350</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>23</v>
+      </c>
+      <c r="G13" t="n">
+        <v>575</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1615</v>
+      </c>
+      <c r="I13" t="n">
+        <v>751</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L13" t="n">
+        <v>86</v>
+      </c>
+      <c r="M13" t="n">
+        <v>70</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>249</v>
+      </c>
+      <c r="R13" t="n">
+        <v>18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2445</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1608</v>
+      </c>
+      <c r="U13" t="n">
+        <v>751</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1248</v>
+      </c>
+      <c r="W13" t="n">
         <v>15</v>
       </c>
-      <c r="G13" t="n">
-        <v>324</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1010</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1115</v>
-      </c>
-      <c r="J13" t="n">
-        <v>844</v>
-      </c>
-      <c r="K13" t="n">
-        <v>145</v>
-      </c>
-      <c r="L13" t="n">
-        <v>25</v>
-      </c>
-      <c r="M13" t="n">
-        <v>28</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>230</v>
-      </c>
-      <c r="R13" t="n">
-        <v>16</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2406</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1266</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1115</v>
-      </c>
-      <c r="V13" t="n">
-        <v>841</v>
-      </c>
-      <c r="W13" t="n">
-        <v>148</v>
-      </c>
       <c r="X13" t="n">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="Y13" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>2406</v>
+        <v>2445</v>
       </c>
       <c r="AF13" t="n">
-        <v>1266</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="14">
@@ -1814,94 +1814,94 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2179</v>
+        <v>3387</v>
       </c>
       <c r="D14" t="n">
-        <v>870</v>
+        <v>1183</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="G14" t="n">
-        <v>1737</v>
+        <v>2971</v>
       </c>
       <c r="H14" t="n">
-        <v>3916</v>
+        <v>6358</v>
       </c>
       <c r="I14" t="n">
-        <v>2948</v>
+        <v>1393</v>
       </c>
       <c r="J14" t="n">
-        <v>5564</v>
+        <v>7134</v>
       </c>
       <c r="K14" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="L14" t="n">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="M14" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>719</v>
+        <v>969</v>
       </c>
       <c r="R14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" t="n">
-        <v>9558</v>
+        <v>9735</v>
       </c>
       <c r="T14" t="n">
-        <v>6511</v>
+        <v>8195</v>
       </c>
       <c r="U14" t="n">
-        <v>2682</v>
+        <v>1394</v>
       </c>
       <c r="V14" t="n">
-        <v>5561</v>
+        <v>7134</v>
       </c>
       <c r="W14" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="X14" t="n">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="Y14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>719</v>
+        <v>969</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>9203</v>
+        <v>9735</v>
       </c>
       <c r="AF14" t="n">
-        <v>6424</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="15">
@@ -1916,31 +1916,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>498</v>
+        <v>750</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="H15" t="n">
-        <v>710</v>
+        <v>1049</v>
       </c>
       <c r="I15" t="n">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="J15" t="n">
-        <v>723</v>
+        <v>891</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1958,25 +1958,25 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="T15" t="n">
-        <v>886</v>
+        <v>1091</v>
       </c>
       <c r="U15" t="n">
-        <v>269</v>
+        <v>99</v>
       </c>
       <c r="V15" t="n">
-        <v>723</v>
+        <v>891</v>
       </c>
       <c r="W15" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1994,16 +1994,16 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="AF15" t="n">
-        <v>886</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="16">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D16" t="n">
         <v>17</v>
@@ -2027,25 +2027,25 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="H16" t="n">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="I16" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="J16" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
@@ -2060,28 +2060,28 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="T16" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="U16" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="V16" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="n">
         <v>3</v>
@@ -2096,16 +2096,16 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AF16" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17">
@@ -2120,40 +2120,40 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>523</v>
+        <v>787</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="G17" t="n">
-        <v>511</v>
+        <v>864</v>
       </c>
       <c r="H17" t="n">
-        <v>1034</v>
+        <v>1651</v>
       </c>
       <c r="I17" t="n">
-        <v>1162</v>
+        <v>815</v>
       </c>
       <c r="J17" t="n">
-        <v>1195</v>
+        <v>1522</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
@@ -2162,34 +2162,34 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>407</v>
+        <v>492</v>
       </c>
       <c r="R17" t="n">
         <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>2805</v>
+        <v>2921</v>
       </c>
       <c r="T17" t="n">
-        <v>1640</v>
+        <v>2106</v>
       </c>
       <c r="U17" t="n">
-        <v>1163</v>
+        <v>815</v>
       </c>
       <c r="V17" t="n">
-        <v>1195</v>
+        <v>1522</v>
       </c>
       <c r="W17" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
         <v>8</v>
@@ -2198,16 +2198,16 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>407</v>
+        <v>492</v>
       </c>
       <c r="AD17" t="n">
         <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>2804</v>
+        <v>2921</v>
       </c>
       <c r="AF17" t="n">
-        <v>1638</v>
+        <v>2106</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,162 +429,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Usaha dalam Keluarga</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,162 +417,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah Usaha dalam Keluarga</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,166 +425,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF17"/>
+  <dimension ref="A1:AO17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Ditemukan</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Tutup</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Ganda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Tidak Ditemukan</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Jumlah Usaha dalam Keluarga</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Baru</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Nonrespon</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Nonrespon</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -679,6 +736,33 @@
       <c r="AF2" t="n">
         <v>0</v>
       </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,94 +776,121 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1836</v>
+        <v>3580</v>
       </c>
       <c r="D3" t="n">
-        <v>121</v>
+        <v>2237</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>3000.26</v>
       </c>
       <c r="F3" t="n">
-        <v>830</v>
+        <v>168</v>
       </c>
       <c r="G3" t="n">
-        <v>877</v>
+        <v>222.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2713</v>
+        <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>643</v>
+        <v>27.18</v>
       </c>
       <c r="J3" t="n">
-        <v>2752</v>
+        <v>888</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>1185.54</v>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>1118</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>1378</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1118</v>
       </c>
       <c r="O3" t="n">
+        <v>1378</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3355</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4378.26</v>
+      </c>
+      <c r="R3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3545</v>
+      </c>
+      <c r="T3" t="n">
+        <v>73</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="n">
         <v>3</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Z3" t="n">
+        <v>770</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4454</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4424</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3533</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>84</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>730</v>
-      </c>
-      <c r="R3" t="n">
-        <v>24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4258</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3560</v>
-      </c>
-      <c r="U3" t="n">
-        <v>643</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2754</v>
-      </c>
-      <c r="W3" t="n">
-        <v>40</v>
-      </c>
-      <c r="X3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>730</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>4258</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>3560</v>
+      <c r="AL3" t="n">
+        <v>770</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>4453</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4423</v>
       </c>
     </row>
     <row r="4">
@@ -794,94 +905,121 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>315</v>
+        <v>651</v>
       </c>
       <c r="D4" t="n">
+        <v>379</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1428.82</v>
+      </c>
+      <c r="F4" t="n">
+        <v>61</v>
+      </c>
+      <c r="G4" t="n">
+        <v>209.62</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="J4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K4" t="n">
+        <v>113.03</v>
+      </c>
+      <c r="L4" t="n">
+        <v>533</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1976.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>533</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1976.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>912</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3405.02</v>
+      </c>
+      <c r="R4" t="n">
         <v>52</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>34</v>
-      </c>
-      <c r="G4" t="n">
-        <v>483</v>
-      </c>
-      <c r="H4" t="n">
-        <v>798</v>
-      </c>
-      <c r="I4" t="n">
-        <v>184</v>
-      </c>
-      <c r="J4" t="n">
-        <v>857</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>199</v>
-      </c>
-      <c r="M4" t="n">
-        <v>22</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
+        <v>1112</v>
+      </c>
+      <c r="T4" t="n">
+        <v>19</v>
+      </c>
+      <c r="U4" t="n">
+        <v>105</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>4</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Y4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>212</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1107</v>
-      </c>
-      <c r="U4" t="n">
-        <v>184</v>
-      </c>
-      <c r="V4" t="n">
-        <v>857</v>
-      </c>
-      <c r="W4" t="n">
-        <v>8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>199</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>22</v>
-      </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="AA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1513</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1112</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>4</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AK4" t="n">
         <v>1</v>
       </c>
-      <c r="AC4" t="n">
-        <v>212</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1490</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1107</v>
+      <c r="AL4" t="n">
+        <v>215</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1513</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1356</v>
       </c>
     </row>
     <row r="5">
@@ -896,94 +1034,121 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1596</v>
+        <v>4351</v>
       </c>
       <c r="D5" t="n">
-        <v>1226</v>
+        <v>1889</v>
       </c>
       <c r="E5" t="n">
+        <v>3267.24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1503</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2390.85</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="J5" t="n">
+        <v>424</v>
+      </c>
+      <c r="K5" t="n">
+        <v>803.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1615</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2969.24</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1615</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2969.24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3504</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6236.45</v>
+      </c>
+      <c r="R5" t="n">
+        <v>112</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5543</v>
+      </c>
+      <c r="T5" t="n">
+        <v>389</v>
+      </c>
+      <c r="U5" t="n">
+        <v>21</v>
+      </c>
+      <c r="V5" t="n">
+        <v>133</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
-        <v>383</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1345</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2941</v>
-      </c>
-      <c r="I5" t="n">
-        <v>957</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4368</v>
-      </c>
-      <c r="K5" t="n">
-        <v>399</v>
-      </c>
-      <c r="L5" t="n">
-        <v>100</v>
-      </c>
-      <c r="M5" t="n">
-        <v>73</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>588</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6487</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5430</v>
-      </c>
-      <c r="U5" t="n">
-        <v>959</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4368</v>
-      </c>
-      <c r="W5" t="n">
-        <v>399</v>
-      </c>
-      <c r="X5" t="n">
-        <v>98</v>
-      </c>
       <c r="Y5" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>6795</v>
       </c>
       <c r="AC5" t="n">
-        <v>588</v>
+        <v>6662</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="AE5" t="n">
-        <v>6487</v>
+        <v>5543</v>
       </c>
       <c r="AF5" t="n">
-        <v>5430</v>
+        <v>388</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>133</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>592</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6795</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6661</v>
       </c>
     </row>
     <row r="6">
@@ -998,94 +1163,121 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1707</v>
+        <v>2762</v>
       </c>
       <c r="D6" t="n">
-        <v>266</v>
+        <v>1955</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>2986.83</v>
       </c>
       <c r="F6" t="n">
-        <v>251</v>
+        <v>312</v>
       </c>
       <c r="G6" t="n">
-        <v>912</v>
+        <v>457.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2619</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>382</v>
+        <v>13.97</v>
       </c>
       <c r="J6" t="n">
-        <v>2276</v>
+        <v>301</v>
       </c>
       <c r="K6" t="n">
-        <v>121</v>
+        <v>453.41</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1072</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>1745.48</v>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>1072</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>1745.48</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3027</v>
       </c>
       <c r="Q6" t="n">
-        <v>488</v>
+        <v>4732.33</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3306</v>
+        <v>3010</v>
       </c>
       <c r="T6" t="n">
-        <v>2924</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2276</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>501</v>
       </c>
       <c r="AA6" t="n">
         <v>4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>3521</v>
       </c>
       <c r="AC6" t="n">
-        <v>488</v>
+        <v>3521</v>
       </c>
       <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3010</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>501</v>
+      </c>
+      <c r="AM6" t="n">
         <v>4</v>
       </c>
-      <c r="AE6" t="n">
-        <v>3306</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2923</v>
+      <c r="AN6" t="n">
+        <v>3521</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3521</v>
       </c>
     </row>
     <row r="7">
@@ -1100,94 +1292,121 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>653</v>
+        <v>1259</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>897</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1766.15</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>178</v>
+        <v>86.49000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>831</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>310</v>
+        <v>1.15</v>
       </c>
       <c r="J7" t="n">
-        <v>694</v>
+        <v>108</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>273.33</v>
       </c>
       <c r="L7" t="n">
+        <v>233</v>
+      </c>
+      <c r="M7" t="n">
+        <v>507.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>233</v>
+      </c>
+      <c r="O7" t="n">
+        <v>507.02</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1130</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2273.13</v>
+      </c>
+      <c r="R7" t="n">
+        <v>102</v>
+      </c>
+      <c r="S7" t="n">
+        <v>952</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="n">
         <v>16</v>
       </c>
-      <c r="M7" t="n">
-        <v>9</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>113</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>119</v>
+      </c>
+      <c r="AA7" t="n">
         <v>7</v>
       </c>
-      <c r="S7" t="n">
-        <v>1158</v>
-      </c>
-      <c r="T7" t="n">
-        <v>832</v>
-      </c>
-      <c r="U7" t="n">
-        <v>310</v>
-      </c>
-      <c r="V7" t="n">
-        <v>694</v>
-      </c>
-      <c r="W7" t="n">
-        <v>8</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AB7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>102</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>952</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH7" t="n">
         <v>16</v>
       </c>
-      <c r="Y7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>113</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>119</v>
+      </c>
+      <c r="AM7" t="n">
         <v>7</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1158</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>832</v>
+      <c r="AN7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="8">
@@ -1202,94 +1421,121 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>277</v>
+        <v>1116</v>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>837.64</v>
       </c>
       <c r="F8" t="n">
-        <v>378</v>
+        <v>162</v>
       </c>
       <c r="G8" t="n">
-        <v>229</v>
+        <v>342.15</v>
       </c>
       <c r="H8" t="n">
-        <v>506</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>280</v>
+        <v>1.92</v>
       </c>
       <c r="J8" t="n">
-        <v>644</v>
+        <v>418</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>781.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>302</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>755.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>302</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>755.05</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="Q8" t="n">
-        <v>133</v>
+        <v>1592.69</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="S8" t="n">
-        <v>1065</v>
+        <v>912</v>
       </c>
       <c r="T8" t="n">
-        <v>784</v>
+        <v>17</v>
       </c>
       <c r="U8" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>644</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>151</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1133</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1086</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>47</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>912</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>133</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>151</v>
+      </c>
+      <c r="AM8" t="n">
         <v>5</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1065</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>784</v>
+      <c r="AN8" t="n">
+        <v>1133</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1086</v>
       </c>
     </row>
     <row r="9">
@@ -1304,94 +1550,121 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1307</v>
+        <v>4396</v>
       </c>
       <c r="D9" t="n">
-        <v>953</v>
+        <v>1847</v>
       </c>
       <c r="E9" t="n">
+        <v>2524.31</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1223</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1603.01</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>108</v>
+      </c>
+      <c r="K9" t="n">
+        <v>158.36</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1235</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1914.69</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1235</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1914.69</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3082</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4438.97</v>
+      </c>
+      <c r="R9" t="n">
+        <v>745</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3557</v>
+      </c>
+      <c r="T9" t="n">
+        <v>205</v>
+      </c>
+      <c r="U9" t="n">
+        <v>52</v>
+      </c>
+      <c r="V9" t="n">
+        <v>228</v>
+      </c>
+      <c r="W9" t="n">
         <v>3</v>
       </c>
-      <c r="F9" t="n">
-        <v>93</v>
-      </c>
-      <c r="G9" t="n">
-        <v>796</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2103</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1630</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2443</v>
-      </c>
-      <c r="K9" t="n">
-        <v>289</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27</v>
-      </c>
-      <c r="M9" t="n">
-        <v>25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>378</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="Z9" t="n">
+        <v>385</v>
+      </c>
+      <c r="AA9" t="n">
         <v>10</v>
       </c>
-      <c r="S9" t="n">
-        <v>4810</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3153</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1630</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2443</v>
-      </c>
-      <c r="W9" t="n">
-        <v>289</v>
-      </c>
-      <c r="X9" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>6</v>
-      </c>
       <c r="AB9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4402</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>748</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3555</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>204</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>52</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>228</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2</v>
       </c>
-      <c r="AC9" t="n">
-        <v>378</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AL9" t="n">
+        <v>385</v>
+      </c>
+      <c r="AM9" t="n">
         <v>10</v>
       </c>
-      <c r="AE9" t="n">
-        <v>4810</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>3153</v>
+      <c r="AN9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>4399</v>
       </c>
     </row>
     <row r="10">
@@ -1406,94 +1679,121 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1904</v>
+        <v>5180</v>
       </c>
       <c r="D10" t="n">
-        <v>1146</v>
+        <v>2507</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>3441.38</v>
       </c>
       <c r="F10" t="n">
-        <v>125</v>
+        <v>1581</v>
       </c>
       <c r="G10" t="n">
-        <v>2320</v>
+        <v>1868.32</v>
       </c>
       <c r="H10" t="n">
-        <v>4224</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>1980</v>
+        <v>20.64</v>
       </c>
       <c r="J10" t="n">
-        <v>3260</v>
+        <v>129</v>
       </c>
       <c r="K10" t="n">
-        <v>296</v>
+        <v>183.85</v>
       </c>
       <c r="L10" t="n">
-        <v>37</v>
+        <v>2932</v>
       </c>
       <c r="M10" t="n">
-        <v>198</v>
+        <v>4517.51</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2932</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4517.51</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5439</v>
       </c>
       <c r="Q10" t="n">
-        <v>577</v>
+        <v>7958.86</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="S10" t="n">
-        <v>6348</v>
+        <v>4117</v>
       </c>
       <c r="T10" t="n">
-        <v>4331</v>
+        <v>780</v>
       </c>
       <c r="U10" t="n">
-        <v>1980</v>
+        <v>113</v>
       </c>
       <c r="V10" t="n">
-        <v>3260</v>
+        <v>336</v>
       </c>
       <c r="W10" t="n">
-        <v>295</v>
+        <v>33</v>
       </c>
       <c r="X10" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>6749</v>
       </c>
       <c r="AC10" t="n">
-        <v>577</v>
+        <v>5894</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="AE10" t="n">
-        <v>6347</v>
+        <v>4117</v>
       </c>
       <c r="AF10" t="n">
-        <v>4330</v>
+        <v>780</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>113</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>335</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>625</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6749</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>5894</v>
       </c>
     </row>
     <row r="11">
@@ -1508,94 +1808,121 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>682</v>
+        <v>1932</v>
       </c>
       <c r="D11" t="n">
-        <v>371</v>
+        <v>893</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>3941.17</v>
       </c>
       <c r="F11" t="n">
-        <v>149</v>
+        <v>491</v>
       </c>
       <c r="G11" t="n">
-        <v>715</v>
+        <v>2023.53</v>
       </c>
       <c r="H11" t="n">
-        <v>1397</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>2620</v>
+        <v>116.18</v>
       </c>
       <c r="J11" t="n">
-        <v>5034</v>
+        <v>166</v>
       </c>
       <c r="K11" t="n">
-        <v>48</v>
+        <v>636.62</v>
       </c>
       <c r="L11" t="n">
-        <v>178</v>
+        <v>885</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>4877.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>885</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>4877.7</v>
       </c>
       <c r="P11" t="n">
+        <v>1778</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8818.9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>980</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6975</v>
+      </c>
+      <c r="T11" t="n">
+        <v>281</v>
+      </c>
+      <c r="U11" t="n">
+        <v>95</v>
+      </c>
+      <c r="V11" t="n">
+        <v>42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>542</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>8450</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5652</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2620</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5034</v>
-      </c>
-      <c r="W11" t="n">
-        <v>48</v>
-      </c>
-      <c r="X11" t="n">
-        <v>176</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>15</v>
-      </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
+        <v>8991</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7916</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>981</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>6975</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>280</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK11" t="n">
         <v>2</v>
       </c>
-      <c r="AC11" t="n">
-        <v>542</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>8448</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>5652</v>
+      <c r="AL11" t="n">
+        <v>580</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>8991</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>7915</v>
       </c>
     </row>
     <row r="12">
@@ -1610,94 +1937,121 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>974</v>
+        <v>1986</v>
       </c>
       <c r="D12" t="n">
-        <v>109</v>
+        <v>1195</v>
       </c>
       <c r="E12" t="n">
+        <v>3834.72</v>
+      </c>
+      <c r="F12" t="n">
+        <v>151</v>
+      </c>
+      <c r="G12" t="n">
+        <v>429.17</v>
+      </c>
+      <c r="H12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="n">
-        <v>269</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1099</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2073</v>
-      </c>
       <c r="I12" t="n">
-        <v>1416</v>
+        <v>32.55</v>
       </c>
       <c r="J12" t="n">
-        <v>3241</v>
+        <v>292</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>927.36</v>
       </c>
       <c r="L12" t="n">
-        <v>148</v>
+        <v>1373</v>
       </c>
       <c r="M12" t="n">
-        <v>55</v>
+        <v>6675.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1373</v>
       </c>
       <c r="O12" t="n">
+        <v>6675.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2568</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10510.59</v>
+      </c>
+      <c r="R12" t="n">
+        <v>432</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4389</v>
+      </c>
+      <c r="T12" t="n">
+        <v>151</v>
+      </c>
+      <c r="U12" t="n">
+        <v>145</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17</v>
+      </c>
+      <c r="W12" t="n">
+        <v>18</v>
+      </c>
+      <c r="X12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>453</v>
-      </c>
-      <c r="R12" t="n">
-        <v>5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5361</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3797</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1418</v>
-      </c>
-      <c r="V12" t="n">
-        <v>3241</v>
-      </c>
-      <c r="W12" t="n">
-        <v>35</v>
-      </c>
-      <c r="X12" t="n">
-        <v>148</v>
-      </c>
       <c r="Y12" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="AA12" t="n">
         <v>6</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>5634</v>
       </c>
       <c r="AC12" t="n">
-        <v>453</v>
+        <v>5057</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>434</v>
       </c>
       <c r="AE12" t="n">
-        <v>5361</v>
+        <v>4389</v>
       </c>
       <c r="AF12" t="n">
-        <v>3795</v>
+        <v>149</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>145</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>468</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>5634</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>5055</v>
       </c>
     </row>
     <row r="13">
@@ -1712,94 +2066,121 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1040</v>
+        <v>2356</v>
       </c>
       <c r="D13" t="n">
-        <v>350</v>
+        <v>1509</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2566.79</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>501</v>
       </c>
       <c r="G13" t="n">
-        <v>575</v>
+        <v>854.4300000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1615</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1250</v>
+        <v>32</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>59.27</v>
       </c>
       <c r="L13" t="n">
-        <v>86</v>
+        <v>920</v>
       </c>
       <c r="M13" t="n">
-        <v>70</v>
+        <v>1528.06</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="O13" t="n">
+        <v>1528.06</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2429</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4094.79</v>
+      </c>
+      <c r="R13" t="n">
+        <v>174</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1652</v>
+      </c>
+      <c r="T13" t="n">
+        <v>152</v>
+      </c>
+      <c r="U13" t="n">
+        <v>54</v>
+      </c>
+      <c r="V13" t="n">
+        <v>134</v>
+      </c>
+      <c r="W13" t="n">
+        <v>34</v>
+      </c>
+      <c r="X13" t="n">
         <v>7</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Y13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>249</v>
-      </c>
-      <c r="R13" t="n">
-        <v>18</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2445</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1608</v>
-      </c>
-      <c r="U13" t="n">
-        <v>751</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1248</v>
-      </c>
-      <c r="W13" t="n">
-        <v>15</v>
-      </c>
-      <c r="X13" t="n">
-        <v>86</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>70</v>
-      </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="AA13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2485</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2257</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>174</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1652</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>152</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>54</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>134</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>7</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
         <v>1</v>
       </c>
-      <c r="AC13" t="n">
-        <v>249</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2445</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1608</v>
+      <c r="AL13" t="n">
+        <v>258</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2485</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2257</v>
       </c>
     </row>
     <row r="14">
@@ -1814,94 +2195,121 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3387</v>
+        <v>6361</v>
       </c>
       <c r="D14" t="n">
-        <v>1183</v>
+        <v>4203</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>6141.73</v>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>1340</v>
       </c>
       <c r="G14" t="n">
-        <v>2971</v>
+        <v>2134.36</v>
       </c>
       <c r="H14" t="n">
-        <v>6358</v>
+        <v>51</v>
       </c>
       <c r="I14" t="n">
-        <v>1393</v>
+        <v>82.12</v>
       </c>
       <c r="J14" t="n">
-        <v>7134</v>
+        <v>113</v>
       </c>
       <c r="K14" t="n">
-        <v>54</v>
+        <v>207.23</v>
       </c>
       <c r="L14" t="n">
-        <v>147</v>
+        <v>3537</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>6494.51</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>3537</v>
       </c>
       <c r="O14" t="n">
-        <v>13</v>
+        <v>6494.51</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>7740</v>
       </c>
       <c r="Q14" t="n">
-        <v>969</v>
+        <v>12636.26</v>
       </c>
       <c r="R14" t="n">
+        <v>149</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8976</v>
+      </c>
+      <c r="T14" t="n">
+        <v>152</v>
+      </c>
+      <c r="U14" t="n">
+        <v>58</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>983</v>
+      </c>
+      <c r="AA14" t="n">
         <v>14</v>
       </c>
-      <c r="S14" t="n">
-        <v>9735</v>
-      </c>
-      <c r="T14" t="n">
-        <v>8195</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1394</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7134</v>
-      </c>
-      <c r="W14" t="n">
-        <v>54</v>
-      </c>
-      <c r="X14" t="n">
-        <v>146</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>13</v>
-      </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>10379</v>
       </c>
       <c r="AC14" t="n">
-        <v>969</v>
+        <v>10172</v>
       </c>
       <c r="AD14" t="n">
+        <v>149</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>8976</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>151</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>59</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>983</v>
+      </c>
+      <c r="AM14" t="n">
         <v>14</v>
       </c>
-      <c r="AE14" t="n">
-        <v>9735</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>8195</v>
+      <c r="AN14" t="n">
+        <v>10379</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>10171</v>
       </c>
     </row>
     <row r="15">
@@ -1916,94 +2324,121 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="D15" t="n">
-        <v>132</v>
+        <v>845</v>
       </c>
       <c r="E15" t="n">
+        <v>1599.18</v>
+      </c>
+      <c r="F15" t="n">
+        <v>143</v>
+      </c>
+      <c r="G15" t="n">
+        <v>265.04</v>
+      </c>
+      <c r="H15" t="n">
         <v>1</v>
       </c>
-      <c r="F15" t="n">
-        <v>32</v>
-      </c>
-      <c r="G15" t="n">
-        <v>299</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1049</v>
-      </c>
       <c r="I15" t="n">
-        <v>99</v>
+        <v>1.89</v>
       </c>
       <c r="J15" t="n">
-        <v>891</v>
+        <v>33</v>
       </c>
       <c r="K15" t="n">
-        <v>25</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>641.46</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>641.46</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1172</v>
       </c>
       <c r="Q15" t="n">
+        <v>2240.64</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1038</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
         <v>175</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1190</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1091</v>
-      </c>
-      <c r="U15" t="n">
-        <v>99</v>
-      </c>
-      <c r="V15" t="n">
-        <v>891</v>
-      </c>
-      <c r="W15" t="n">
-        <v>25</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1215</v>
       </c>
       <c r="AC15" t="n">
+        <v>1215</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1038</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
         <v>175</v>
       </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1190</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1091</v>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1215</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1215</v>
       </c>
     </row>
     <row r="16">
@@ -2018,94 +2453,121 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>117</v>
+        <v>338</v>
       </c>
       <c r="D16" t="n">
+        <v>129</v>
+      </c>
+      <c r="E16" t="n">
+        <v>297.37</v>
+      </c>
+      <c r="F16" t="n">
         <v>17</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
+        <v>41</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="F16" t="n">
+      <c r="I16" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="J16" t="n">
         <v>40</v>
       </c>
-      <c r="G16" t="n">
-        <v>208</v>
-      </c>
-      <c r="H16" t="n">
-        <v>325</v>
-      </c>
-      <c r="I16" t="n">
-        <v>213</v>
-      </c>
-      <c r="J16" t="n">
-        <v>375</v>
-      </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>89.42</v>
       </c>
       <c r="L16" t="n">
-        <v>9</v>
+        <v>216</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>545.1899999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>545.1899999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Q16" t="n">
+        <v>842.55</v>
+      </c>
+      <c r="R16" t="n">
+        <v>184</v>
+      </c>
+      <c r="S16" t="n">
+        <v>408</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>17</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
         <v>25</v>
       </c>
-      <c r="R16" t="n">
+      <c r="AA16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
-        <v>626</v>
-      </c>
-      <c r="T16" t="n">
-        <v>404</v>
-      </c>
-      <c r="U16" t="n">
-        <v>213</v>
-      </c>
-      <c r="V16" t="n">
-        <v>375</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="AC16" t="n">
+        <v>435</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>184</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>408</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
         <v>25</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AM16" t="n">
         <v>1</v>
       </c>
-      <c r="AE16" t="n">
-        <v>626</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>404</v>
+      <c r="AN16" t="n">
+        <v>636</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>435</v>
       </c>
     </row>
     <row r="17">
@@ -2120,94 +2582,121 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>787</v>
+        <v>1947</v>
       </c>
       <c r="D17" t="n">
-        <v>163</v>
+        <v>1220</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>2041.85</v>
       </c>
       <c r="F17" t="n">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="G17" t="n">
-        <v>864</v>
+        <v>349.18</v>
       </c>
       <c r="H17" t="n">
-        <v>1651</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>815</v>
+        <v>21.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1522</v>
+        <v>189</v>
       </c>
       <c r="K17" t="n">
-        <v>53</v>
+        <v>327.63</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="M17" t="n">
+        <v>2569.24</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1155</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2569.24</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2375</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4611.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>275</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2176</v>
+      </c>
+      <c r="T17" t="n">
+        <v>11</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>10</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>516</v>
+      </c>
+      <c r="AA17" t="n">
         <v>4</v>
       </c>
-      <c r="N17" t="n">
-        <v>24</v>
-      </c>
-      <c r="O17" t="n">
-        <v>8</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>492</v>
-      </c>
-      <c r="R17" t="n">
-        <v>3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2921</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2106</v>
-      </c>
-      <c r="U17" t="n">
-        <v>815</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1522</v>
-      </c>
-      <c r="W17" t="n">
-        <v>53</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
+        <v>3009</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2734</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>276</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2176</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>516</v>
+      </c>
+      <c r="AM17" t="n">
         <v>4</v>
       </c>
-      <c r="Z17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>492</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2921</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2106</v>
+      <c r="AN17" t="n">
+        <v>3009</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2733</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_USAHA KELUARGA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,211 +413,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO17"/>
+  <dimension ref="A1:AF17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Jumlah Prelist Usaha Keluarga (ST2023 + UMKM)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ditemukan</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Ditemukan</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tutup</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Tutup</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Ganda</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Ganda</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Tidak Ditemukan</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Baru</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Baru</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Nonrespon</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>JUMLAH USAHA KELUARGA MENURUT STATUS KEBERADAAN USAHA - Persentase Nonrespon</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Jumlah Usaha dalam Keluarga (Ditemukan + Baru)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Persentase Usaha dalam Keluarga (Ditemukan + Baru)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Jumlah Usaha dalam Keluarga</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -736,33 +679,6 @@
       <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -776,121 +692,94 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3580</v>
+        <v>1836</v>
       </c>
       <c r="D3" t="n">
-        <v>2237</v>
+        <v>121</v>
       </c>
       <c r="E3" t="n">
-        <v>3000.26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>168</v>
+        <v>830</v>
       </c>
       <c r="G3" t="n">
-        <v>222.4</v>
+        <v>877</v>
       </c>
       <c r="H3" t="n">
-        <v>27</v>
+        <v>2713</v>
       </c>
       <c r="I3" t="n">
-        <v>27.18</v>
+        <v>643</v>
       </c>
       <c r="J3" t="n">
-        <v>888</v>
+        <v>2752</v>
       </c>
       <c r="K3" t="n">
-        <v>1185.54</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>1118</v>
+        <v>55</v>
       </c>
       <c r="M3" t="n">
-        <v>1378</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>1118</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1378</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>3355</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4378.26</v>
+        <v>730</v>
       </c>
       <c r="R3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S3" t="n">
-        <v>3545</v>
+        <v>4258</v>
       </c>
       <c r="T3" t="n">
-        <v>73</v>
+        <v>3560</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>643</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2754</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="X3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y3" t="n">
         <v>5</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" t="n">
         <v>3</v>
       </c>
-      <c r="Z3" t="n">
-        <v>770</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>4454</v>
-      </c>
       <c r="AC3" t="n">
-        <v>4424</v>
+        <v>730</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>3533</v>
+        <v>4258</v>
       </c>
       <c r="AF3" t="n">
-        <v>84</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>770</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>4453</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>4423</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="4">
@@ -905,121 +794,94 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>651</v>
+        <v>315</v>
       </c>
       <c r="D4" t="n">
-        <v>379</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>1428.82</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>209.62</v>
+        <v>483</v>
       </c>
       <c r="H4" t="n">
+        <v>798</v>
+      </c>
+      <c r="I4" t="n">
+        <v>184</v>
+      </c>
+      <c r="J4" t="n">
+        <v>857</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>199</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="J4" t="n">
-        <v>36</v>
-      </c>
-      <c r="K4" t="n">
-        <v>113.03</v>
-      </c>
-      <c r="L4" t="n">
-        <v>533</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1976.2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>533</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1976.2</v>
-      </c>
       <c r="P4" t="n">
-        <v>912</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3405.02</v>
+        <v>212</v>
       </c>
       <c r="R4" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>1112</v>
+        <v>1490</v>
       </c>
       <c r="T4" t="n">
-        <v>19</v>
+        <v>1107</v>
       </c>
       <c r="U4" t="n">
-        <v>105</v>
+        <v>184</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
+        <v>199</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>4</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>1</v>
       </c>
-      <c r="Z4" t="n">
-        <v>215</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1513</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1356</v>
+        <v>212</v>
       </c>
       <c r="AD4" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1112</v>
+        <v>1490</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>105</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>215</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1513</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1356</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="5">
@@ -1034,121 +896,94 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4351</v>
+        <v>1596</v>
       </c>
       <c r="D5" t="n">
-        <v>1889</v>
+        <v>1226</v>
       </c>
       <c r="E5" t="n">
-        <v>3267.24</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1503</v>
+        <v>383</v>
       </c>
       <c r="G5" t="n">
-        <v>2390.85</v>
+        <v>1345</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>2941</v>
       </c>
       <c r="I5" t="n">
-        <v>10.59</v>
+        <v>957</v>
       </c>
       <c r="J5" t="n">
-        <v>424</v>
+        <v>4368</v>
       </c>
       <c r="K5" t="n">
-        <v>803.6</v>
+        <v>399</v>
       </c>
       <c r="L5" t="n">
-        <v>1615</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>2969.24</v>
+        <v>73</v>
       </c>
       <c r="N5" t="n">
-        <v>1615</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2969.24</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3504</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6236.45</v>
+        <v>588</v>
       </c>
       <c r="R5" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>5543</v>
+        <v>6487</v>
       </c>
       <c r="T5" t="n">
-        <v>389</v>
+        <v>5430</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>959</v>
       </c>
       <c r="V5" t="n">
-        <v>133</v>
+        <v>4368</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Z5" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>6795</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>6662</v>
+        <v>588</v>
       </c>
       <c r="AD5" t="n">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>5543</v>
+        <v>6487</v>
       </c>
       <c r="AF5" t="n">
-        <v>388</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>133</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>592</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>6795</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>6661</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="6">
@@ -1163,121 +998,94 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2762</v>
+        <v>1707</v>
       </c>
       <c r="D6" t="n">
-        <v>1955</v>
+        <v>266</v>
       </c>
       <c r="E6" t="n">
-        <v>2986.83</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>312</v>
+        <v>251</v>
       </c>
       <c r="G6" t="n">
-        <v>457.75</v>
+        <v>912</v>
       </c>
       <c r="H6" t="n">
+        <v>2619</v>
+      </c>
+      <c r="I6" t="n">
+        <v>382</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2276</v>
+      </c>
+      <c r="K6" t="n">
+        <v>121</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>9</v>
       </c>
-      <c r="I6" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="J6" t="n">
-        <v>301</v>
-      </c>
-      <c r="K6" t="n">
-        <v>453.41</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1072</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1745.48</v>
-      </c>
       <c r="N6" t="n">
-        <v>1072</v>
+        <v>22</v>
       </c>
       <c r="O6" t="n">
-        <v>1745.48</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>3027</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4732.33</v>
+        <v>488</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>3010</v>
+        <v>3306</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2924</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2276</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>501</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
         <v>4</v>
       </c>
       <c r="AB6" t="n">
-        <v>3521</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3521</v>
+        <v>488</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>3010</v>
+        <v>3306</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>501</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>3521</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>3521</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="7">
@@ -1292,121 +1100,94 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1259</v>
+        <v>653</v>
       </c>
       <c r="D7" t="n">
-        <v>897</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>1766.15</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>86.49000000000001</v>
+        <v>178</v>
       </c>
       <c r="H7" t="n">
+        <v>831</v>
+      </c>
+      <c r="I7" t="n">
+        <v>310</v>
+      </c>
+      <c r="J7" t="n">
+        <v>694</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>16</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J7" t="n">
-        <v>108</v>
-      </c>
-      <c r="K7" t="n">
-        <v>273.33</v>
-      </c>
-      <c r="L7" t="n">
-        <v>233</v>
-      </c>
-      <c r="M7" t="n">
-        <v>507.02</v>
-      </c>
-      <c r="N7" t="n">
-        <v>233</v>
-      </c>
-      <c r="O7" t="n">
-        <v>507.02</v>
-      </c>
       <c r="P7" t="n">
-        <v>1130</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2273.13</v>
+        <v>113</v>
       </c>
       <c r="R7" t="n">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>952</v>
+        <v>1158</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>832</v>
       </c>
       <c r="U7" t="n">
+        <v>310</v>
+      </c>
+      <c r="V7" t="n">
+        <v>694</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8</v>
+      </c>
+      <c r="X7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>113</v>
+      </c>
+      <c r="AD7" t="n">
         <v>7</v>
       </c>
-      <c r="V7" t="n">
-        <v>16</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>119</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1209</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1100</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>102</v>
-      </c>
       <c r="AE7" t="n">
-        <v>952</v>
+        <v>1158</v>
       </c>
       <c r="AF7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>119</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1209</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1100</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -1421,121 +1202,94 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1116</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>837.64</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>162</v>
+        <v>378</v>
       </c>
       <c r="G8" t="n">
-        <v>342.15</v>
+        <v>229</v>
       </c>
       <c r="H8" t="n">
+        <v>506</v>
+      </c>
+      <c r="I8" t="n">
+        <v>280</v>
+      </c>
+      <c r="J8" t="n">
+        <v>644</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="J8" t="n">
-        <v>418</v>
-      </c>
-      <c r="K8" t="n">
-        <v>781.5</v>
-      </c>
       <c r="L8" t="n">
-        <v>302</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>755.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>302</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>755.05</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>691</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1592.69</v>
+        <v>133</v>
       </c>
       <c r="R8" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>912</v>
+        <v>1065</v>
       </c>
       <c r="T8" t="n">
-        <v>17</v>
+        <v>784</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>133</v>
+      </c>
+      <c r="AD8" t="n">
         <v>5</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1133</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1086</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>47</v>
-      </c>
       <c r="AE8" t="n">
-        <v>912</v>
+        <v>1065</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>151</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1133</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1086</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9">
@@ -1550,121 +1304,94 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4396</v>
+        <v>1307</v>
       </c>
       <c r="D9" t="n">
-        <v>1847</v>
+        <v>953</v>
       </c>
       <c r="E9" t="n">
-        <v>2524.31</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>1223</v>
+        <v>93</v>
       </c>
       <c r="G9" t="n">
-        <v>1603.01</v>
+        <v>796</v>
       </c>
       <c r="H9" t="n">
+        <v>2103</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1630</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2443</v>
+      </c>
+      <c r="K9" t="n">
+        <v>289</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>6</v>
       </c>
-      <c r="I9" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="J9" t="n">
-        <v>108</v>
-      </c>
-      <c r="K9" t="n">
-        <v>158.36</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1235</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1914.69</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1235</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1914.69</v>
-      </c>
       <c r="P9" t="n">
-        <v>3082</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4438.97</v>
+        <v>378</v>
       </c>
       <c r="R9" t="n">
-        <v>745</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>3557</v>
+        <v>4810</v>
       </c>
       <c r="T9" t="n">
-        <v>205</v>
+        <v>3153</v>
       </c>
       <c r="U9" t="n">
-        <v>52</v>
+        <v>1630</v>
       </c>
       <c r="V9" t="n">
-        <v>228</v>
+        <v>2443</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>289</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2</v>
       </c>
-      <c r="Z9" t="n">
-        <v>385</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
+        <v>378</v>
+      </c>
+      <c r="AD9" t="n">
         <v>10</v>
       </c>
-      <c r="AB9" t="n">
-        <v>5199</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4402</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>748</v>
-      </c>
       <c r="AE9" t="n">
-        <v>3555</v>
+        <v>4810</v>
       </c>
       <c r="AF9" t="n">
-        <v>204</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>52</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>228</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>385</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>5199</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>4399</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="10">
@@ -1679,121 +1406,94 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5180</v>
+        <v>1904</v>
       </c>
       <c r="D10" t="n">
-        <v>2507</v>
+        <v>1146</v>
       </c>
       <c r="E10" t="n">
-        <v>3441.38</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>1581</v>
+        <v>125</v>
       </c>
       <c r="G10" t="n">
-        <v>1868.32</v>
+        <v>2320</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>4224</v>
       </c>
       <c r="I10" t="n">
-        <v>20.64</v>
+        <v>1980</v>
       </c>
       <c r="J10" t="n">
-        <v>129</v>
+        <v>3260</v>
       </c>
       <c r="K10" t="n">
-        <v>183.85</v>
+        <v>296</v>
       </c>
       <c r="L10" t="n">
-        <v>2932</v>
+        <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>4517.51</v>
+        <v>198</v>
       </c>
       <c r="N10" t="n">
-        <v>2932</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4517.51</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>5439</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7958.86</v>
+        <v>577</v>
       </c>
       <c r="R10" t="n">
-        <v>742</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4117</v>
+        <v>6348</v>
       </c>
       <c r="T10" t="n">
-        <v>780</v>
+        <v>4331</v>
       </c>
       <c r="U10" t="n">
-        <v>113</v>
+        <v>1980</v>
       </c>
       <c r="V10" t="n">
-        <v>336</v>
+        <v>3260</v>
       </c>
       <c r="W10" t="n">
-        <v>33</v>
+        <v>295</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="Z10" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>6749</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5894</v>
+        <v>577</v>
       </c>
       <c r="AD10" t="n">
-        <v>742</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>4117</v>
+        <v>6347</v>
       </c>
       <c r="AF10" t="n">
-        <v>780</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>113</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>335</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>33</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>625</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>6749</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>5894</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="11">
@@ -1808,121 +1508,94 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1932</v>
+        <v>682</v>
       </c>
       <c r="D11" t="n">
-        <v>893</v>
+        <v>371</v>
       </c>
       <c r="E11" t="n">
-        <v>3941.17</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>491</v>
+        <v>149</v>
       </c>
       <c r="G11" t="n">
-        <v>2023.53</v>
+        <v>715</v>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>1397</v>
       </c>
       <c r="I11" t="n">
-        <v>116.18</v>
+        <v>2620</v>
       </c>
       <c r="J11" t="n">
-        <v>166</v>
+        <v>5034</v>
       </c>
       <c r="K11" t="n">
-        <v>636.62</v>
+        <v>48</v>
       </c>
       <c r="L11" t="n">
-        <v>885</v>
+        <v>178</v>
       </c>
       <c r="M11" t="n">
-        <v>4877.7</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>885</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4877.7</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>1778</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>8818.9</v>
+        <v>542</v>
       </c>
       <c r="R11" t="n">
-        <v>980</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>6975</v>
+        <v>8450</v>
       </c>
       <c r="T11" t="n">
-        <v>281</v>
+        <v>5652</v>
       </c>
       <c r="U11" t="n">
-        <v>95</v>
+        <v>2620</v>
       </c>
       <c r="V11" t="n">
-        <v>42</v>
+        <v>5034</v>
       </c>
       <c r="W11" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>176</v>
       </c>
       <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2</v>
       </c>
-      <c r="Z11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>8991</v>
-      </c>
       <c r="AC11" t="n">
-        <v>7916</v>
+        <v>542</v>
       </c>
       <c r="AD11" t="n">
-        <v>981</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>6975</v>
+        <v>8448</v>
       </c>
       <c r="AF11" t="n">
-        <v>280</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>8991</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>7915</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="12">
@@ -1937,121 +1610,94 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1986</v>
+        <v>974</v>
       </c>
       <c r="D12" t="n">
-        <v>1195</v>
+        <v>109</v>
       </c>
       <c r="E12" t="n">
-        <v>3834.72</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>151</v>
+        <v>269</v>
       </c>
       <c r="G12" t="n">
-        <v>429.17</v>
+        <v>1099</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>2073</v>
       </c>
       <c r="I12" t="n">
-        <v>32.55</v>
+        <v>1416</v>
       </c>
       <c r="J12" t="n">
-        <v>292</v>
+        <v>3241</v>
       </c>
       <c r="K12" t="n">
-        <v>927.36</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
-        <v>1373</v>
+        <v>148</v>
       </c>
       <c r="M12" t="n">
-        <v>6675.9</v>
+        <v>55</v>
       </c>
       <c r="N12" t="n">
-        <v>1373</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6675.9</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>2568</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>10510.59</v>
+        <v>453</v>
       </c>
       <c r="R12" t="n">
-        <v>432</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>4389</v>
+        <v>5361</v>
       </c>
       <c r="T12" t="n">
-        <v>151</v>
+        <v>3797</v>
       </c>
       <c r="U12" t="n">
-        <v>145</v>
+        <v>1418</v>
       </c>
       <c r="V12" t="n">
-        <v>17</v>
+        <v>3241</v>
       </c>
       <c r="W12" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>148</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="Z12" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>6</v>
       </c>
       <c r="AB12" t="n">
-        <v>5634</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5057</v>
+        <v>453</v>
       </c>
       <c r="AD12" t="n">
-        <v>434</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>4389</v>
+        <v>5361</v>
       </c>
       <c r="AF12" t="n">
-        <v>149</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>145</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>468</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>5634</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>5055</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="13">
@@ -2066,121 +1712,94 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2356</v>
+        <v>1040</v>
       </c>
       <c r="D13" t="n">
-        <v>1509</v>
+        <v>350</v>
       </c>
       <c r="E13" t="n">
-        <v>2566.79</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>854.4300000000001</v>
+        <v>575</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1615</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="J13" t="n">
-        <v>32</v>
+        <v>1250</v>
       </c>
       <c r="K13" t="n">
-        <v>59.27</v>
+        <v>13</v>
       </c>
       <c r="L13" t="n">
-        <v>920</v>
+        <v>86</v>
       </c>
       <c r="M13" t="n">
-        <v>1528.06</v>
+        <v>70</v>
       </c>
       <c r="N13" t="n">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1528.06</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>2429</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>4094.79</v>
+        <v>249</v>
       </c>
       <c r="R13" t="n">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="S13" t="n">
-        <v>1652</v>
+        <v>2445</v>
       </c>
       <c r="T13" t="n">
-        <v>152</v>
+        <v>1608</v>
       </c>
       <c r="U13" t="n">
-        <v>54</v>
+        <v>751</v>
       </c>
       <c r="V13" t="n">
-        <v>134</v>
+        <v>1248</v>
       </c>
       <c r="W13" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="X13" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>1</v>
       </c>
-      <c r="Z13" t="n">
-        <v>258</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2485</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2257</v>
+        <v>249</v>
       </c>
       <c r="AD13" t="n">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1652</v>
+        <v>2445</v>
       </c>
       <c r="AF13" t="n">
-        <v>152</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>54</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>134</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>258</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2485</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>2257</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="14">
@@ -2195,121 +1814,94 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6361</v>
+        <v>3387</v>
       </c>
       <c r="D14" t="n">
-        <v>4203</v>
+        <v>1183</v>
       </c>
       <c r="E14" t="n">
-        <v>6141.73</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>1340</v>
+        <v>90</v>
       </c>
       <c r="G14" t="n">
-        <v>2134.36</v>
+        <v>2971</v>
       </c>
       <c r="H14" t="n">
-        <v>51</v>
+        <v>6358</v>
       </c>
       <c r="I14" t="n">
-        <v>82.12</v>
+        <v>1393</v>
       </c>
       <c r="J14" t="n">
-        <v>113</v>
+        <v>7134</v>
       </c>
       <c r="K14" t="n">
-        <v>207.23</v>
+        <v>54</v>
       </c>
       <c r="L14" t="n">
-        <v>3537</v>
+        <v>147</v>
       </c>
       <c r="M14" t="n">
-        <v>6494.51</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>3537</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>6494.51</v>
+        <v>13</v>
       </c>
       <c r="P14" t="n">
-        <v>7740</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>12636.26</v>
+        <v>969</v>
       </c>
       <c r="R14" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="S14" t="n">
-        <v>8976</v>
+        <v>9735</v>
       </c>
       <c r="T14" t="n">
-        <v>152</v>
+        <v>8195</v>
       </c>
       <c r="U14" t="n">
-        <v>58</v>
+        <v>1394</v>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
+        <v>7134</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="X14" t="n">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>983</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>969</v>
+      </c>
+      <c r="AD14" t="n">
         <v>14</v>
       </c>
-      <c r="AB14" t="n">
-        <v>10379</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>10172</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>149</v>
-      </c>
       <c r="AE14" t="n">
-        <v>8976</v>
+        <v>9735</v>
       </c>
       <c r="AF14" t="n">
-        <v>151</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>59</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>983</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>10379</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>10171</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="15">
@@ -2324,121 +1916,94 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1050</v>
+        <v>750</v>
       </c>
       <c r="D15" t="n">
-        <v>845</v>
+        <v>132</v>
       </c>
       <c r="E15" t="n">
-        <v>1599.18</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>143</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>265.04</v>
+        <v>299</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>1049</v>
       </c>
       <c r="I15" t="n">
-        <v>1.89</v>
+        <v>99</v>
       </c>
       <c r="J15" t="n">
-        <v>33</v>
+        <v>891</v>
       </c>
       <c r="K15" t="n">
-        <v>76.34999999999999</v>
+        <v>25</v>
       </c>
       <c r="L15" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>641.46</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>641.46</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1172</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2240.64</v>
+        <v>175</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1038</v>
+        <v>1190</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1091</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>891</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
         <v>175</v>
       </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1215</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1215</v>
-      </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1038</v>
+        <v>1190</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>175</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1215</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1215</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="16">
@@ -2453,121 +2018,94 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>338</v>
+        <v>117</v>
       </c>
       <c r="D16" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
-        <v>297.37</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>41</v>
+        <v>208</v>
       </c>
       <c r="H16" t="n">
+        <v>325</v>
+      </c>
+      <c r="I16" t="n">
+        <v>213</v>
+      </c>
+      <c r="J16" t="n">
+        <v>375</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>25</v>
+      </c>
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="J16" t="n">
-        <v>40</v>
-      </c>
-      <c r="K16" t="n">
-        <v>89.42</v>
-      </c>
-      <c r="L16" t="n">
-        <v>216</v>
-      </c>
-      <c r="M16" t="n">
-        <v>545.1899999999999</v>
-      </c>
-      <c r="N16" t="n">
-        <v>216</v>
-      </c>
-      <c r="O16" t="n">
-        <v>545.1899999999999</v>
-      </c>
-      <c r="P16" t="n">
-        <v>345</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>842.55</v>
-      </c>
-      <c r="R16" t="n">
-        <v>184</v>
-      </c>
       <c r="S16" t="n">
-        <v>408</v>
+        <v>626</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="V16" t="n">
+        <v>375</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1</v>
       </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>636</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>435</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>184</v>
-      </c>
       <c r="AE16" t="n">
-        <v>408</v>
+        <v>626</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>636</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>435</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17">
@@ -2582,121 +2120,94 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1947</v>
+        <v>787</v>
       </c>
       <c r="D17" t="n">
-        <v>1220</v>
+        <v>163</v>
       </c>
       <c r="E17" t="n">
-        <v>2041.85</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>215</v>
+        <v>171</v>
       </c>
       <c r="G17" t="n">
-        <v>349.18</v>
+        <v>864</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>1651</v>
       </c>
       <c r="I17" t="n">
-        <v>21.5</v>
+        <v>815</v>
       </c>
       <c r="J17" t="n">
-        <v>189</v>
+        <v>1522</v>
       </c>
       <c r="K17" t="n">
-        <v>327.63</v>
+        <v>53</v>
       </c>
       <c r="L17" t="n">
-        <v>1155</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2569.24</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>1155</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
-        <v>2569.24</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>2375</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4611.1</v>
+        <v>492</v>
       </c>
       <c r="R17" t="n">
-        <v>275</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>2176</v>
+        <v>2921</v>
       </c>
       <c r="T17" t="n">
-        <v>11</v>
+        <v>2106</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>1522</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="n">
-        <v>516</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
-        <v>3009</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2734</v>
+        <v>492</v>
       </c>
       <c r="AD17" t="n">
-        <v>276</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>2176</v>
+        <v>2921</v>
       </c>
       <c r="AF17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>516</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>3009</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>2733</v>
+        <v>2106</v>
       </c>
     </row>
   </sheetData>
